--- a/app/templates/Subir auditoria/Subir Agregados/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/Subir auditoria/Subir Agregados/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -31625,7 +31625,11 @@
       <c r="E11" s="830"/>
       <c r="F11" s="829"/>
       <c r="G11" s="830"/>
-      <c r="H11" s="738"/>
+      <c r="H11" s="738" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I11" s="726"/>
       <c r="L11" s="285" t="s">
         <v>450</v>
@@ -38614,8 +38618,10 @@
       <c r="B9" s="439" t="s">
         <v>333</v>
       </c>
-      <c r="C9" s="885" t="s">
-        <v>345</v>
+      <c r="C9" s="885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="886"/>
       <c r="F9" s="580" t="s">
@@ -38634,12 +38640,16 @@
       <c r="B10" s="439" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="885" t="s">
-        <v>345</v>
+      <c r="C10" s="885" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="886"/>
-      <c r="F10" s="708" t="s">
-        <v>345</v>
+      <c r="F10" s="708" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G10" s="470">
         <f>+FORMATO!H11</f>

--- a/app/templates/Subir auditoria/Subir Agregados/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
+++ b/app/templates/Subir auditoria/Subir Agregados/1-INF.-N-000-26-AG19-GRAN.-V10.xlsx
@@ -38651,10 +38651,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="470">
-        <f>+FORMATO!H11</f>
-        <v>0</v>
-      </c>
+      <c r="G10" s="470"/>
       <c r="H10" s="470"/>
       <c r="I10" s="470"/>
       <c r="J10" s="470"/>
@@ -38749,7 +38746,7 @@
         <v>285</v>
       </c>
       <c r="H14" s="538">
-        <f>+FORMATO!D35</f>
+        <f>+IF(C10="Global",FORMATO!D21,FORMATO!D35)</f>
         <v>0</v>
       </c>
       <c r="I14" s="442">
@@ -38783,7 +38780,7 @@
         <v>286</v>
       </c>
       <c r="H15" s="539">
-        <f>+FORMATO!D37</f>
+        <f>+IF(C10="Global",FORMATO!D22,FORMATO!D36)</f>
         <v>0</v>
       </c>
       <c r="I15" s="444">
